--- a/Shared/XLS/Skin.xlsx
+++ b/Shared/XLS/Skin.xlsx
@@ -592,7 +592,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Skin.xlsx
+++ b/Shared/XLS/Skin.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>!Table</t>
   </si>
@@ -92,10 +92,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Class_Basic</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>CollectionStatType</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -128,18 +124,6 @@
   </si>
   <si>
     <t>마검사 스킨2</t>
-  </si>
-  <si>
-    <t>Class_Knight</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Berserker</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_RuneBlader</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>AOC_Hero_01</t>
@@ -592,7 +576,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -642,10 +626,10 @@
         <v>10</v>
       </c>
       <c r="G2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -666,7 +650,7 @@
         <v>11</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>6</v>
@@ -680,11 +664,8 @@
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -695,13 +676,10 @@
         <v>1001</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3"/>
     </row>
@@ -710,13 +688,10 @@
         <v>1002</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3"/>
     </row>
@@ -725,13 +700,10 @@
         <v>2001</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3"/>
     </row>
@@ -740,13 +712,10 @@
         <v>2002</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3"/>
     </row>
@@ -755,14 +724,11 @@
         <v>3001</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="F9" s="9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3"/>
     </row>
@@ -772,13 +738,10 @@
         <v>3002</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>26</v>
       </c>
       <c r="G10" s="3"/>
     </row>
